--- a/modelling/AETModelTable.xlsx
+++ b/modelling/AETModelTable.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/average-effort/code/modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F816B5DA-9D29-2D49-8D30-A1B85C78C28A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D308CE-5FCF-EB4C-8454-22B9F91F062A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19160" yWindow="4160" windowWidth="16960" windowHeight="16320" xr2:uid="{1D0F2510-A469-FB44-876C-9C1C19D62FE8}"/>
+    <workbookView xWindow="46260" yWindow="-8320" windowWidth="16960" windowHeight="16320" xr2:uid="{1D0F2510-A469-FB44-876C-9C1C19D62FE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_11" localSheetId="0" hidden="1">Sheet1!$B$1:$B$7</definedName>
+    <definedName name="ExternalData_11" localSheetId="0" hidden="1">Sheet1!$B$1:$B$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
   <si>
     <t>modelNumber</t>
   </si>
@@ -101,6 +101,18 @@
   </si>
   <si>
     <t>additive_original</t>
+  </si>
+  <si>
+    <t>exerted</t>
+  </si>
+  <si>
+    <t>exerted_tau</t>
+  </si>
+  <si>
+    <t>reward</t>
+  </si>
+  <si>
+    <t>reward_tau</t>
   </si>
 </sst>
 </file>
@@ -136,8 +148,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -185,8 +198,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7BDF1FCE-1986-C943-8A17-4DB71A10CD53}" name="Merge__5" displayName="Merge__5" ref="A1:C7" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:C7" xr:uid="{7BDF1FCE-1986-C943-8A17-4DB71A10CD53}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7BDF1FCE-1986-C943-8A17-4DB71A10CD53}" name="Merge__5" displayName="Merge__5" ref="A1:C11" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:C11" xr:uid="{7BDF1FCE-1986-C943-8A17-4DB71A10CD53}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="weight"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="3">
     <tableColumn id="8" xr3:uid="{B77D1067-AEBD-514F-9503-0D81C848CB3D}" uniqueName="8" name="modelNumber" queryTableFieldId="7" dataDxfId="2"/>
     <tableColumn id="1" xr3:uid="{D30B166C-25D0-6246-A11C-717B94039F85}" uniqueName="1" name="learnFunction" queryTableFieldId="1" dataDxfId="1"/>
@@ -493,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5F9FBC9-49A6-ED4F-85B9-12A8A4BFF838}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -511,7 +530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -533,7 +552,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -544,7 +563,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -566,7 +585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -575,6 +594,50 @@
       </c>
       <c r="C7" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/modelling/AETModelTable.xlsx
+++ b/modelling/AETModelTable.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/average-effort/code/modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D308CE-5FCF-EB4C-8454-22B9F91F062A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48450549-81D6-FD46-B31C-C0C8E90FF80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46260" yWindow="-8320" windowWidth="16960" windowHeight="16320" xr2:uid="{1D0F2510-A469-FB44-876C-9C1C19D62FE8}"/>
+    <workbookView xWindow="38400" yWindow="500" windowWidth="28800" windowHeight="18000" xr2:uid="{1D0F2510-A469-FB44-876C-9C1C19D62FE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_11" localSheetId="0" hidden="1">Sheet1!$B$1:$B$11</definedName>
+    <definedName name="ExternalData_11" localSheetId="0" hidden="1">Sheet1!$B$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
   <si>
     <t>modelNumber</t>
   </si>
@@ -94,25 +94,19 @@
     <t>weight</t>
   </si>
   <si>
-    <t>additive</t>
-  </si>
-  <si>
-    <t>expected_tau</t>
-  </si>
-  <si>
-    <t>additive_original</t>
-  </si>
-  <si>
     <t>exerted</t>
   </si>
   <si>
-    <t>exerted_tau</t>
-  </si>
-  <si>
     <t>reward</t>
   </si>
   <si>
-    <t>reward_tau</t>
+    <t>fixed</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>response_history</t>
   </si>
 </sst>
 </file>
@@ -148,9 +142,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -198,14 +191,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7BDF1FCE-1986-C943-8A17-4DB71A10CD53}" name="Merge__5" displayName="Merge__5" ref="A1:C11" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:C11" xr:uid="{7BDF1FCE-1986-C943-8A17-4DB71A10CD53}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="weight"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7BDF1FCE-1986-C943-8A17-4DB71A10CD53}" name="Merge__5" displayName="Merge__5" ref="A1:C7" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:C7" xr:uid="{7BDF1FCE-1986-C943-8A17-4DB71A10CD53}"/>
   <tableColumns count="3">
     <tableColumn id="8" xr3:uid="{B77D1067-AEBD-514F-9503-0D81C848CB3D}" uniqueName="8" name="modelNumber" queryTableFieldId="7" dataDxfId="2"/>
     <tableColumn id="1" xr3:uid="{D30B166C-25D0-6246-A11C-717B94039F85}" uniqueName="1" name="learnFunction" queryTableFieldId="1" dataDxfId="1"/>
@@ -512,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5F9FBC9-49A6-ED4F-85B9-12A8A4BFF838}">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -530,7 +517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -538,7 +525,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -546,32 +533,32 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -579,65 +566,21 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/modelling/AETModelTable.xlsx
+++ b/modelling/AETModelTable.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/average-effort/code/modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48450549-81D6-FD46-B31C-C0C8E90FF80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07976DDE-C2FF-254D-85CB-7A19761256E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="500" windowWidth="28800" windowHeight="18000" xr2:uid="{1D0F2510-A469-FB44-876C-9C1C19D62FE8}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{1D0F2510-A469-FB44-876C-9C1C19D62FE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_11" localSheetId="0" hidden="1">Sheet1!$B$1:$B$7</definedName>
+    <definedName name="ExternalData_11" localSheetId="0" hidden="1">Sheet1!$B$1:$B$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="14">
   <si>
     <t>modelNumber</t>
   </si>
@@ -107,6 +107,18 @@
   </si>
   <si>
     <t>response_history</t>
+  </si>
+  <si>
+    <t>dummy</t>
+  </si>
+  <si>
+    <t>credits</t>
+  </si>
+  <si>
+    <t>weight_k</t>
+  </si>
+  <si>
+    <t>real</t>
   </si>
 </sst>
 </file>
@@ -142,13 +154,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -173,11 +189,12 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_11" connectionId="5" xr16:uid="{6D006E7E-60B8-FD4C-8C48-87001BF70BC5}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="24" unboundColumnsLeft="1" unboundColumnsRight="1">
-    <queryTableFields count="3">
+  <queryTableRefresh nextId="25" unboundColumnsLeft="1" unboundColumnsRight="2">
+    <queryTableFields count="4">
       <queryTableField id="7" dataBound="0" tableColumnId="8"/>
       <queryTableField id="1" name="offerDiscountFunction" tableColumnId="1"/>
       <queryTableField id="19" dataBound="0" tableColumnId="3"/>
+      <queryTableField id="24" dataBound="0" tableColumnId="2"/>
     </queryTableFields>
     <queryTableDeletedFields count="5">
       <deletedField name="lastEffortWeight"/>
@@ -191,12 +208,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7BDF1FCE-1986-C943-8A17-4DB71A10CD53}" name="Merge__5" displayName="Merge__5" ref="A1:C7" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:C7" xr:uid="{7BDF1FCE-1986-C943-8A17-4DB71A10CD53}"/>
-  <tableColumns count="3">
-    <tableColumn id="8" xr3:uid="{B77D1067-AEBD-514F-9503-0D81C848CB3D}" uniqueName="8" name="modelNumber" queryTableFieldId="7" dataDxfId="2"/>
-    <tableColumn id="1" xr3:uid="{D30B166C-25D0-6246-A11C-717B94039F85}" uniqueName="1" name="learnFunction" queryTableFieldId="1" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{FB35ADC3-CAE6-8747-A818-B473D89BA4F5}" uniqueName="3" name="discountFunction" queryTableFieldId="19" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7BDF1FCE-1986-C943-8A17-4DB71A10CD53}" name="Merge__5" displayName="Merge__5" ref="A1:D23" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:D23" xr:uid="{7BDF1FCE-1986-C943-8A17-4DB71A10CD53}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="expected"/>
+        <filter val="fixed"/>
+        <filter val="response_history"/>
+        <filter val="reward"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="4">
+    <tableColumn id="8" xr3:uid="{B77D1067-AEBD-514F-9503-0D81C848CB3D}" uniqueName="8" name="modelNumber" queryTableFieldId="7" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{D30B166C-25D0-6246-A11C-717B94039F85}" uniqueName="1" name="learnFunction" queryTableFieldId="1" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{FB35ADC3-CAE6-8747-A818-B473D89BA4F5}" uniqueName="3" name="discountFunction" queryTableFieldId="19" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{EA99AB95-0F68-9642-92D9-67DA3F77DF44}" uniqueName="2" name="reward" queryTableFieldId="24" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -499,14 +526,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5F9FBC9-49A6-ED4F-85B9-12A8A4BFF838}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -516,8 +543,11 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -527,8 +557,11 @@
       <c r="C2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -538,41 +571,53 @@
       <c r="C3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -580,7 +625,234 @@
         <v>2</v>
       </c>
       <c r="C7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/modelling/AETModelTable.xlsx
+++ b/modelling/AETModelTable.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/average-effort/code/modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07976DDE-C2FF-254D-85CB-7A19761256E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0614407-1C24-1F47-B6F6-AAAC32A080C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{1D0F2510-A469-FB44-876C-9C1C19D62FE8}"/>
+    <workbookView xWindow="-28620" yWindow="14900" windowWidth="28800" windowHeight="16320" xr2:uid="{1D0F2510-A469-FB44-876C-9C1C19D62FE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_11" localSheetId="0" hidden="1">Sheet1!$B$1:$B$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$25</definedName>
+    <definedName name="ExternalData_11" localSheetId="0" hidden="1">Sheet1!$B$1:$B$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30,7 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="9">
   <si>
     <t>modelNumber</t>
   </si>
@@ -94,31 +94,16 @@
     <t>weight</t>
   </si>
   <si>
-    <t>exerted</t>
-  </si>
-  <si>
-    <t>reward</t>
-  </si>
-  <si>
-    <t>fixed</t>
-  </si>
-  <si>
     <t>none</t>
   </si>
   <si>
     <t>response_history</t>
   </si>
   <si>
-    <t>dummy</t>
-  </si>
-  <si>
-    <t>credits</t>
-  </si>
-  <si>
-    <t>weight_k</t>
-  </si>
-  <si>
     <t>real</t>
+  </si>
+  <si>
+    <t>bias</t>
   </si>
 </sst>
 </file>
@@ -154,27 +139,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -187,52 +158,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_11" connectionId="5" xr16:uid="{6D006E7E-60B8-FD4C-8C48-87001BF70BC5}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="25" unboundColumnsLeft="1" unboundColumnsRight="2">
-    <queryTableFields count="4">
-      <queryTableField id="7" dataBound="0" tableColumnId="8"/>
-      <queryTableField id="1" name="offerDiscountFunction" tableColumnId="1"/>
-      <queryTableField id="19" dataBound="0" tableColumnId="3"/>
-      <queryTableField id="24" dataBound="0" tableColumnId="2"/>
-    </queryTableFields>
-    <queryTableDeletedFields count="5">
-      <deletedField name="lastEffortWeight"/>
-      <deletedField name="Bias"/>
-      <deletedField name="backgroundFunction"/>
-      <deletedField name="Fatigue"/>
-      <deletedField name="learnBackground"/>
-    </queryTableDeletedFields>
-  </queryTableRefresh>
-</queryTable>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7BDF1FCE-1986-C943-8A17-4DB71A10CD53}" name="Merge__5" displayName="Merge__5" ref="A1:D23" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:D23" xr:uid="{7BDF1FCE-1986-C943-8A17-4DB71A10CD53}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="expected"/>
-        <filter val="fixed"/>
-        <filter val="response_history"/>
-        <filter val="reward"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <tableColumns count="4">
-    <tableColumn id="8" xr3:uid="{B77D1067-AEBD-514F-9503-0D81C848CB3D}" uniqueName="8" name="modelNumber" queryTableFieldId="7" dataDxfId="3"/>
-    <tableColumn id="1" xr3:uid="{D30B166C-25D0-6246-A11C-717B94039F85}" uniqueName="1" name="learnFunction" queryTableFieldId="1" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{FB35ADC3-CAE6-8747-A818-B473D89BA4F5}" uniqueName="3" name="discountFunction" queryTableFieldId="19" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{EA99AB95-0F68-9642-92D9-67DA3F77DF44}" uniqueName="2" name="reward" queryTableFieldId="24" dataDxfId="0"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -270,7 +199,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -376,7 +305,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -518,7 +447,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -526,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5F9FBC9-49A6-ED4F-85B9-12A8A4BFF838}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -544,7 +473,7 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -558,21 +487,21 @@
         <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -580,13 +509,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -594,13 +523,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -608,13 +537,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -622,27 +551,27 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -650,13 +579,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -664,13 +593,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
@@ -678,13 +607,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -692,13 +621,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C12" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
@@ -706,161 +635,18 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" t="s">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 

--- a/modelling/AETModelTable.xlsx
+++ b/modelling/AETModelTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/average-effort/code/modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0614407-1C24-1F47-B6F6-AAAC32A080C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087A5A4D-A91B-AA49-876C-02DC1C70C49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28620" yWindow="14900" windowWidth="28800" windowHeight="16320" xr2:uid="{1D0F2510-A469-FB44-876C-9C1C19D62FE8}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{1D0F2510-A469-FB44-876C-9C1C19D62FE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="10">
   <si>
     <t>modelNumber</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>bias</t>
+  </si>
+  <si>
+    <t>no_k</t>
   </si>
 </sst>
 </file>
@@ -159,9 +162,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -199,7 +202,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -305,7 +308,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -447,7 +450,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -455,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5F9FBC9-49A6-ED4F-85B9-12A8A4BFF838}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
@@ -644,6 +647,20 @@
         <v>8</v>
       </c>
     </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/modelling/AETModelTable.xlsx
+++ b/modelling/AETModelTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/average-effort/code/modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{087A5A4D-A91B-AA49-876C-02DC1C70C49A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE4483C-7FF2-DF48-979C-035957E838FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16320" xr2:uid="{1D0F2510-A469-FB44-876C-9C1C19D62FE8}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$25</definedName>
     <definedName name="ExternalData_11" localSheetId="0" hidden="1">Sheet1!$B$1:$B$1</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -31,6 +31,7 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -77,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
   <si>
     <t>modelNumber</t>
   </si>
@@ -91,22 +92,13 @@
     <t>learnFunction</t>
   </si>
   <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
     <t>response_history</t>
   </si>
   <si>
     <t>real</t>
   </si>
   <si>
-    <t>bias</t>
-  </si>
-  <si>
-    <t>no_k</t>
+    <t>linear</t>
   </si>
 </sst>
 </file>
@@ -458,14 +450,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5F9FBC9-49A6-ED4F-85B9-12A8A4BFF838}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -475,11 +467,8 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="2" spans="1:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -487,178 +476,29 @@
         <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
